--- a/excel rad izmenjen/sifrarnik-paket/SPC_atributivne.xlsx
+++ b/excel rad izmenjen/sifrarnik-paket/SPC_atributivne.xlsx
@@ -8303,7 +8303,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8354,7 +8354,7 @@
         <v>5502-A</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>G</v>
       </c>
       <c r="C2" t="str">
         <v>RN-2024-002</v>
@@ -8363,13 +8363,13 @@
         <v>Osovina</v>
       </c>
       <c r="E2" t="str">
-        <v>Kontrola kvaliteta</v>
+        <v>Merljive kontrola</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
-        <v>1</v>
+      <c r="G2" t="str">
+        <v/>
       </c>
       <c r="H2">
         <v>100</v>
@@ -8381,7 +8381,7 @@
         <v>DA</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Pogon G — Masinska obrada</v>
       </c>
       <c r="L2" t="str">
         <v>deo</v>
@@ -8439,43 +8439,43 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>MRAP-001</v>
+        <v>DEMO-001</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>B</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>RN-2026-DEMO001</v>
       </c>
       <c r="D4" t="str">
-        <v>MRAP komplet</v>
+        <v>Test nosač — demo</v>
       </c>
       <c r="E4" t="str">
-        <v>Finalna vizuelna kontrola celog vozila</v>
-      </c>
-      <c r="F4" t="str">
-        <v>48</v>
-      </c>
-      <c r="G4" t="str">
-        <v>1</v>
-      </c>
-      <c r="H4" t="str">
-        <v>5</v>
+        <v>Laser sečenje</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>50</v>
       </c>
       <c r="I4" t="str">
-        <v>MRAP_SOP.jpg</v>
+        <v>DEMO-01.png</v>
       </c>
       <c r="J4" t="str">
         <v>DA</v>
       </c>
       <c r="K4" t="str">
-        <v>MRAP — oklopno vozilo</v>
+        <v>Pogon B — Preseraj</v>
       </c>
       <c r="L4" t="str">
-        <v>vozilo</v>
+        <v>deo</v>
       </c>
       <c r="M4" t="str">
-        <v>MRAP</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -8483,43 +8483,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MRAP1-001</v>
+        <v>DEMO-001</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>F</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>RN-2026-DEMO001-F</v>
       </c>
       <c r="D5" t="str">
-        <v>MRAP1 komplet</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>Finalna vizuelna kontrola celog vozila</v>
-      </c>
-      <c r="F5" t="str">
-        <v>48</v>
+        <v>Završna kontrola</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
       </c>
       <c r="G5" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>MRAP1_SOP.jpg</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v>DA</v>
       </c>
       <c r="K5" t="str">
-        <v>MRAP1 — oklopno vozilo 6x6</v>
+        <v>Pogon F — Završna</v>
       </c>
       <c r="L5" t="str">
-        <v>vozilo</v>
+        <v>deo</v>
       </c>
       <c r="M5" t="str">
-        <v>MRAP1</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -8527,43 +8527,43 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>NM-001</v>
+        <v>MRAP-001</v>
       </c>
       <c r="B6" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>RN-2026-NM001</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>Nosač motora</v>
+        <v>MRAP komplet</v>
       </c>
       <c r="E6" t="str">
-        <v>Geometrijska kontrola</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="F6" t="str">
+        <v>48</v>
       </c>
       <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>5</v>
       </c>
       <c r="I6" t="str">
-        <v>NM-01.png</v>
+        <v>MRAP_SOP.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>DA</v>
       </c>
       <c r="K6" t="str">
-        <v>Atributivne — Karoserija</v>
+        <v>MRAP — oklopno vozilo</v>
       </c>
       <c r="L6" t="str">
-        <v>deo</v>
+        <v>vozilo</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>MRAP</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -8571,43 +8571,43 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>NT-001</v>
+        <v>MRAP1-001</v>
       </c>
       <c r="B7" t="str">
-        <v>A</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>RN-2026-NT001-A</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>Nosač motora</v>
+        <v>MRAP1 komplet</v>
       </c>
       <c r="E7" t="str">
-        <v>Vizuelna kontrola ulazna</v>
-      </c>
-      <c r="F7">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="F7" t="str">
+        <v>48</v>
+      </c>
+      <c r="G7" t="str">
         <v>1</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7">
-        <v>50</v>
+      <c r="H7" t="str">
+        <v>5</v>
       </c>
       <c r="I7" t="str">
-        <v>nosac motora NTV.png</v>
+        <v>MRAP1_SOP.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>DA</v>
       </c>
       <c r="K7" t="str">
-        <v>Atributivne — Ulazna</v>
+        <v>MRAP1 — oklopno vozilo 6x6</v>
       </c>
       <c r="L7" t="str">
-        <v>deo</v>
+        <v>vozilo</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>MRAP1</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -8615,37 +8615,37 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>NT-001</v>
+        <v>NM-001</v>
       </c>
       <c r="B8" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="C8" t="str">
-        <v>RN-2026-NT001-C</v>
+        <v>RN-2026-NM001</v>
       </c>
       <c r="D8" t="str">
         <v>Nosač motora</v>
       </c>
       <c r="E8" t="str">
-        <v>Zavarivanje</v>
+        <v>Vizuelna kontrola ulazna</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I8" t="str">
-        <v>nosac motora NTV.png</v>
+        <v>NM-01.png</v>
       </c>
       <c r="J8" t="str">
         <v>DA</v>
       </c>
       <c r="K8" t="str">
-        <v>Atributivne — Karoserija</v>
+        <v>Pogon A — Ulazna kontrola</v>
       </c>
       <c r="L8" t="str">
         <v>deo</v>
@@ -8659,37 +8659,37 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>NT-001</v>
+        <v>NM-001</v>
       </c>
       <c r="B9" t="str">
-        <v>F</v>
+        <v>B</v>
       </c>
       <c r="C9" t="str">
-        <v>RN-2026-NT001-F</v>
+        <v>RN-2026-NM001</v>
       </c>
       <c r="D9" t="str">
         <v>Nosač motora</v>
       </c>
       <c r="E9" t="str">
-        <v>Završna kontrola</v>
+        <v>Laser sečenje</v>
       </c>
       <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" t="str">
-        <v>nosac motora NTV.png</v>
+        <v>NM-01.png</v>
       </c>
       <c r="J9" t="str">
         <v>DA</v>
       </c>
       <c r="K9" t="str">
-        <v>Atributivne — Finalna</v>
+        <v>Pogon B — Preseraj</v>
       </c>
       <c r="L9" t="str">
         <v>deo</v>
@@ -8703,51 +8703,315 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NTV-001</v>
+        <v>NM-001</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>C</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>RN-2026-NM001</v>
       </c>
       <c r="D10" t="str">
-        <v>NTV komplet</v>
+        <v>Nosač motora</v>
       </c>
       <c r="E10" t="str">
-        <v>Finalna vizuelna kontrola celog vozila</v>
-      </c>
-      <c r="F10" t="str">
-        <v>48</v>
+        <v>Geometrijska kontrola</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
       </c>
       <c r="G10" t="str">
-        <v>1</v>
-      </c>
-      <c r="H10" t="str">
-        <v>5</v>
+        <v/>
+      </c>
+      <c r="H10">
+        <v>100</v>
       </c>
       <c r="I10" t="str">
-        <v>NTV_SOP.jpg</v>
+        <v>NM-01.png</v>
       </c>
       <c r="J10" t="str">
         <v>DA</v>
       </c>
       <c r="K10" t="str">
+        <v>Atributivne — Karoserija</v>
+      </c>
+      <c r="L10" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>F</v>
+      </c>
+      <c r="C11" t="str">
+        <v>RN-2026-NM001</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Završna kontrola</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11" t="str">
+        <v>NM-01.png</v>
+      </c>
+      <c r="J11" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Pogon F — Završna</v>
+      </c>
+      <c r="L11" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>NT-001</v>
+      </c>
+      <c r="B12" t="str">
+        <v>A</v>
+      </c>
+      <c r="C12" t="str">
+        <v>RN-2026-NT001-A</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Vizuelna kontrola ulazna</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12" t="str">
+        <v>nosac motora NTV.png</v>
+      </c>
+      <c r="J12" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Atributivne — Ulazna</v>
+      </c>
+      <c r="L12" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NT-001</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B</v>
+      </c>
+      <c r="C13" t="str">
+        <v>RN-2026-NT001-B</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Laser sečenje</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>50</v>
+      </c>
+      <c r="I13" t="str">
+        <v>nosac motora NTV.png</v>
+      </c>
+      <c r="J13" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Pogon B — Preseraj</v>
+      </c>
+      <c r="L13" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>NT-001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>C</v>
+      </c>
+      <c r="C14" t="str">
+        <v>RN-2026-NT001-C</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Zavarivanje</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14">
+        <v>50</v>
+      </c>
+      <c r="I14" t="str">
+        <v>nosac motora NTV.png</v>
+      </c>
+      <c r="J14" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Atributivne — Karoserija</v>
+      </c>
+      <c r="L14" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>NT-001</v>
+      </c>
+      <c r="B15" t="str">
+        <v>F</v>
+      </c>
+      <c r="C15" t="str">
+        <v>RN-2026-NT001-F</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Završna kontrola</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15">
+        <v>50</v>
+      </c>
+      <c r="I15" t="str">
+        <v>nosac motora NTV.png</v>
+      </c>
+      <c r="J15" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Atributivne — Finalna</v>
+      </c>
+      <c r="L15" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>NTV-001</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>NTV komplet</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="F16" t="str">
+        <v>48</v>
+      </c>
+      <c r="G16" t="str">
+        <v>1</v>
+      </c>
+      <c r="H16" t="str">
+        <v>5</v>
+      </c>
+      <c r="I16" t="str">
+        <v>NTV_SOP.jpg</v>
+      </c>
+      <c r="J16" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K16" t="str">
         <v>NTV — novo terensko vozilo</v>
       </c>
-      <c r="L10" t="str">
+      <c r="L16" t="str">
         <v>vozilo</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M16" t="str">
         <v>NTV</v>
       </c>
-      <c r="N10" t="str">
+      <c r="N16" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/excel rad izmenjen/sifrarnik-paket/SPC_atributivne.xlsx
+++ b/excel rad izmenjen/sifrarnik-paket/SPC_atributivne.xlsx
@@ -17,6 +17,9 @@
     <sheet name="kontrolna_lista_stavke" sheetId="12" r:id="rId12"/>
     <sheet name="merila" sheetId="13" r:id="rId13"/>
     <sheet name="kalibracije" sheetId="14" r:id="rId14"/>
+    <sheet name="tipovi_vozila" sheetId="15" r:id="rId15"/>
+    <sheet name="kategorije_vozila" sheetId="16" r:id="rId16"/>
+    <sheet name="delovi_vozila" sheetId="17" r:id="rId17"/>
   </sheets>
 </workbook>
 </file>
@@ -2105,6 +2108,1794 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>kod</v>
+      </c>
+      <c r="B1" t="str">
+        <v>naziv</v>
+      </c>
+      <c r="C1" t="str">
+        <v>prefiks_id_deo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>slika_sop</v>
+      </c>
+      <c r="E1" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="F1" t="str">
+        <v>napomena</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B2" t="str">
+        <v>NTV novo terensko vozilo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="D2" t="str">
+        <v>NTV_SOP.jpg</v>
+      </c>
+      <c r="E2" t="str">
+        <v>DA</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Finalna kontrola celog vozila</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MRAP oklopno vozilo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="D3" t="str">
+        <v>MRAP_SOP.jpg</v>
+      </c>
+      <c r="E3" t="str">
+        <v>DA</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Finalna kontrola celog vozila</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MRAP1 oklopno vozilo 6×6</v>
+      </c>
+      <c r="C4" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>MRAP1_SOP.jpg</v>
+      </c>
+      <c r="E4" t="str">
+        <v>DA</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Finalna kontrola celog vozila</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E91"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>vozilo_kod</v>
+      </c>
+      <c r="B1" t="str">
+        <v>zona_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>zona_naziv</v>
+      </c>
+      <c r="D1" t="str">
+        <v>kategorija</v>
+      </c>
+      <c r="E1" t="str">
+        <v>podkategorija</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D2" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Elektrika</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B3" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Rasveta</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B4" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B5" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D5" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B6" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D6" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D7" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Ostalo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B8" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Instrument tabla</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B9" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Centralna konzola</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B10" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Sedište vozača</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B11" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B12" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D12" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B13" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Enterijer</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B14" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D14" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Prednji branik</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B15" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D15" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Hauba</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B16" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D16" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B17" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D17" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B18" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D18" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B19" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D19" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B20" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D20" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B21" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D21" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B22" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D22" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B23" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D23" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B24" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D24" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Zadnji branik</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B25" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D25" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B26" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D26" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Krov</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B27" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D27" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Vetrobran</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B28" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D28" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Bočna stakla</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B29" t="str">
+        <v>MOTOR-001</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Motor</v>
+      </c>
+      <c r="D29" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Motorni prostor</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D30" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Podvozje</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D31" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D32" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Elektrika</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D33" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Rasveta</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B34" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D34" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D35" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B36" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D36" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D37" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Ostalo</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D38" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Instrument tabla</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Centralna konzola</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B40" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D40" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Sedište vozača</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B41" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D41" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B42" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D43" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Enterijer</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B44" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D44" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Prednji branik</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B45" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D45" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Hauba</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B46" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D46" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B47" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D47" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B48" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D48" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B49" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D49" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B50" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D50" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B51" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D51" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B52" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D52" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B53" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D53" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B54" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D54" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Zadnji branik</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B55" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D55" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B56" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D56" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Krov</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B57" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D57" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Vetrobran</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B58" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D58" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Bočna stakla</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B59" t="str">
+        <v>MOTOR-001</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Motor</v>
+      </c>
+      <c r="D59" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Motorni prostor</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B60" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D60" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Podvozje</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="B61" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D61" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B62" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D62" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Elektrika</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B63" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D63" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Rasveta</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B64" t="str">
+        <v>EL-001</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D64" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B65" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D65" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B66" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D66" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B67" t="str">
+        <v>FINAL-001</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Finalna kontrola</v>
+      </c>
+      <c r="D67" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Ostalo</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B68" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D68" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Instrument tabla</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B69" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D69" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Centralna konzola</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B70" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D70" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Sedište vozača</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B71" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D71" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B72" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D72" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B73" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D73" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Enterijer</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B74" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D74" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Prednji branik</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B75" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D75" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Hauba</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B76" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D76" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B77" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D77" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B78" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D78" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B79" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D79" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B80" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D80" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B81" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D81" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B82" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D82" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B83" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D83" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B84" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D84" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Zadnji branik</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B85" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D85" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B86" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D86" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Krov</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B87" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D87" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Vetrobran</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B88" t="str">
+        <v>KAROS-001</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Karoserija</v>
+      </c>
+      <c r="D88" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Bočna stakla</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B89" t="str">
+        <v>MOTOR-001</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Motor</v>
+      </c>
+      <c r="D89" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Motorni prostor</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B90" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D90" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Podvozje</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="B91" t="str">
+        <v>TRANS-001</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Transmisija</v>
+      </c>
+      <c r="D91" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E91"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id delo*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>naziv dela*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>vozilo katalog id</v>
+      </c>
+      <c r="D1" t="str">
+        <v>karakteristika kontrole*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>linija id*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>masina id*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>kom za kontrolu n*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>slika/crtez</v>
+      </c>
+      <c r="I1" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J1" t="str">
+        <v>napomena</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>MRAP-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MRAP komplet</v>
+      </c>
+      <c r="C2" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="E2" t="str">
+        <v>48</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H2" t="str">
+        <v>MRAP_SOP.jpg</v>
+      </c>
+      <c r="I2" t="str">
+        <v>DA</v>
+      </c>
+      <c r="J2" t="str">
+        <v>MRAP — oklopno vozilo</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MRAP1-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MRAP1 komplet</v>
+      </c>
+      <c r="C3" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="E3" t="str">
+        <v>48</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>5</v>
+      </c>
+      <c r="H3" t="str">
+        <v>MRAP1_SOP.jpg</v>
+      </c>
+      <c r="I3" t="str">
+        <v>DA</v>
+      </c>
+      <c r="J3" t="str">
+        <v>MRAP1 — oklopno vozilo 6x6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>NTV-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>NTV komplet</v>
+      </c>
+      <c r="C4" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="E4" t="str">
+        <v>48</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <v>NTV_SOP.jpg</v>
+      </c>
+      <c r="I4" t="str">
+        <v>DA</v>
+      </c>
+      <c r="J4" t="str">
+        <v>NTV — novo terensko vozilo</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
@@ -3530,7 +5321,7 @@
         <v>Levo prednje krilo</v>
       </c>
       <c r="D12" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="13">
@@ -3572,7 +5363,7 @@
         <v>Desno prednje krilo</v>
       </c>
       <c r="D15" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="16">
@@ -3614,7 +5405,7 @@
         <v>Leva prednja vrata</v>
       </c>
       <c r="D18" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="19">
@@ -3670,7 +5461,7 @@
         <v>Desna prednja vrata</v>
       </c>
       <c r="D22" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="23">
@@ -3726,7 +5517,7 @@
         <v>Leva zadnja vrata</v>
       </c>
       <c r="D26" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="27">
@@ -3978,7 +5769,7 @@
         <v>Zadnji branik</v>
       </c>
       <c r="D44" t="str">
-        <v>ogrebotine pri dnu,</v>
+        <v>ogrebotine pri dnu</v>
       </c>
     </row>
     <row r="45">
@@ -4006,7 +5797,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D46" t="str">
-        <v>Teško zatvaranje,</v>
+        <v>Teško zatvaranje</v>
       </c>
     </row>
     <row r="47">
@@ -4034,7 +5825,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D48" t="str">
-        <v>visinska odstupanja,</v>
+        <v>visinska odstupanja</v>
       </c>
     </row>
     <row r="49">
@@ -4160,7 +5951,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D57" t="str">
-        <v>Ogrebotine od podizanja/spuštanja,</v>
+        <v>Ogrebotine od podizanja/spuštanja</v>
       </c>
     </row>
     <row r="58">
@@ -4174,7 +5965,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D58" t="str">
-        <v>zazor pri zatvaranju (prolaz vazduha),</v>
+        <v>zazor pri zatvaranju (prolaz vazduha)</v>
       </c>
     </row>
     <row r="59">
@@ -4202,7 +5993,7 @@
         <v>Motorni prostor</v>
       </c>
       <c r="D60" t="str">
-        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona)</v>
       </c>
     </row>
     <row r="61">
@@ -4258,7 +6049,7 @@
         <v>Podvozje</v>
       </c>
       <c r="D64" t="str">
-        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
+        <v>Curenje tečnosti na spojevima (menjač, karter)</v>
       </c>
     </row>
     <row r="65">
@@ -4314,7 +6105,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D68" t="str">
-        <v>Ogrebotine na alu-felnama, ,</v>
+        <v>Ogrebotine na alu-felnama</v>
       </c>
     </row>
     <row r="69">
@@ -4328,7 +6119,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D69" t="str">
-        <v>pogrešan smer rotacije gume,</v>
+        <v>pogrešan smer rotacije gume</v>
       </c>
     </row>
     <row r="70">
@@ -4370,7 +6161,7 @@
         <v>Instrument tabla</v>
       </c>
       <c r="D72" t="str">
-        <v>Loš zazor na spojevima plastika,, , .</v>
+        <v>Loš zazor na spojevima plastika, .</v>
       </c>
     </row>
     <row r="73">
@@ -4426,7 +6217,7 @@
         <v>Centralna konzola</v>
       </c>
       <c r="D76" t="str">
-        <v>Labavost naslona za ruku, , ,.</v>
+        <v>Labavost naslona za ruku, .</v>
       </c>
     </row>
     <row r="77">
@@ -4482,7 +6273,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D80" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="81">
@@ -4510,7 +6301,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D82" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="83">
@@ -4538,7 +6329,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D84" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="85">
@@ -4566,7 +6357,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D86" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="87">
@@ -4594,7 +6385,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D88" t="str">
-        <v>Loše fiksiran donji deo klupe,</v>
+        <v>Loše fiksiran donji deo klupe</v>
       </c>
     </row>
     <row r="89">
@@ -4608,7 +6399,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D89" t="str">
-        <v>problem sa preklapanjem naslona,</v>
+        <v>problem sa preklapanjem naslona</v>
       </c>
     </row>
     <row r="90">
@@ -4636,7 +6427,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D91" t="str">
-        <v>Oštećenja tapacirunga krova (nebo),</v>
+        <v>Oštećenja tapacirunga krova (nebo)</v>
       </c>
     </row>
     <row r="92">
@@ -4650,7 +6441,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D92" t="str">
-        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+        <v>ogrebotine na oblogama stubova (A, B, C)</v>
       </c>
     </row>
     <row r="93">
@@ -4664,7 +6455,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D93" t="str">
-        <v>labavi rukohvati na krovu,</v>
+        <v>labavi rukohvati na krovu</v>
       </c>
     </row>
     <row r="94">
@@ -4692,7 +6483,7 @@
         <v>Elektrika</v>
       </c>
       <c r="D95" t="str">
-        <v>Greška na instrument tabli, , ,</v>
+        <v>Greška na instrument tabli</v>
       </c>
     </row>
     <row r="96">
@@ -4748,7 +6539,7 @@
         <v>Rasveta</v>
       </c>
       <c r="D99" t="str">
-        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla</v>
       </c>
     </row>
     <row r="100">
@@ -4818,7 +6609,7 @@
         <v>Kamere i senzori</v>
       </c>
       <c r="D104" t="str">
-        <v>Labavost parking senzora (upali unutra), ,</v>
+        <v>Labavost parking senzora (upali unutra)</v>
       </c>
     </row>
     <row r="105">
@@ -4860,7 +6651,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D107" t="str">
-        <v>Labav pod gepeka, ,</v>
+        <v>Labav pod gepeka</v>
       </c>
     </row>
     <row r="108">
@@ -4888,7 +6679,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D109" t="str">
-        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica)</v>
       </c>
     </row>
     <row r="110">
@@ -4916,7 +6707,7 @@
         <v>Funkcionalni test</v>
       </c>
       <c r="D111" t="str">
-        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+        <v>Loš odziv multimedije (ekrana na dodir), .</v>
       </c>
     </row>
     <row r="112">
@@ -4972,7 +6763,7 @@
         <v>Ostalo</v>
       </c>
       <c r="D115" t="str">
-        <v>Prljavština na vozilu,, , .</v>
+        <v>Prljavština na vozilu, .</v>
       </c>
     </row>
     <row r="116">
@@ -5168,7 +6959,7 @@
         <v>Levo prednje krilo</v>
       </c>
       <c r="D129" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="130">
@@ -5210,7 +7001,7 @@
         <v>Desno prednje krilo</v>
       </c>
       <c r="D132" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="133">
@@ -5252,7 +7043,7 @@
         <v>Leva prednja vrata</v>
       </c>
       <c r="D135" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="136">
@@ -5308,7 +7099,7 @@
         <v>Desna prednja vrata</v>
       </c>
       <c r="D139" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="140">
@@ -5364,7 +7155,7 @@
         <v>Leva zadnja vrata</v>
       </c>
       <c r="D143" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="144">
@@ -5616,7 +7407,7 @@
         <v>Zadnji branik</v>
       </c>
       <c r="D161" t="str">
-        <v>ogrebotine pri dnu,</v>
+        <v>ogrebotine pri dnu</v>
       </c>
     </row>
     <row r="162">
@@ -5644,7 +7435,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D163" t="str">
-        <v>Teško zatvaranje,</v>
+        <v>Teško zatvaranje</v>
       </c>
     </row>
     <row r="164">
@@ -5672,7 +7463,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D165" t="str">
-        <v>visinska odstupanja,</v>
+        <v>visinska odstupanja</v>
       </c>
     </row>
     <row r="166">
@@ -5798,7 +7589,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D174" t="str">
-        <v>Ogrebotine od podizanja/spuštanja,</v>
+        <v>Ogrebotine od podizanja/spuštanja</v>
       </c>
     </row>
     <row r="175">
@@ -5812,7 +7603,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D175" t="str">
-        <v>zazor pri zatvaranju (prolaz vazduha),</v>
+        <v>zazor pri zatvaranju (prolaz vazduha)</v>
       </c>
     </row>
     <row r="176">
@@ -5840,7 +7631,7 @@
         <v>Motorni prostor</v>
       </c>
       <c r="D177" t="str">
-        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona)</v>
       </c>
     </row>
     <row r="178">
@@ -5896,7 +7687,7 @@
         <v>Podvozje</v>
       </c>
       <c r="D181" t="str">
-        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
+        <v>Curenje tečnosti na spojevima (menjač, karter)</v>
       </c>
     </row>
     <row r="182">
@@ -5952,7 +7743,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D185" t="str">
-        <v>Ogrebotine na alu-felnama, ,</v>
+        <v>Ogrebotine na alu-felnama</v>
       </c>
     </row>
     <row r="186">
@@ -5966,7 +7757,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D186" t="str">
-        <v>pogrešan smer rotacije gume,</v>
+        <v>pogrešan smer rotacije gume</v>
       </c>
     </row>
     <row r="187">
@@ -6008,7 +7799,7 @@
         <v>Instrument tabla</v>
       </c>
       <c r="D189" t="str">
-        <v>Loš zazor na spojevima plastika,, , .</v>
+        <v>Loš zazor na spojevima plastika, .</v>
       </c>
     </row>
     <row r="190">
@@ -6064,7 +7855,7 @@
         <v>Centralna konzola</v>
       </c>
       <c r="D193" t="str">
-        <v>Labavost naslona za ruku, , ,.</v>
+        <v>Labavost naslona za ruku, .</v>
       </c>
     </row>
     <row r="194">
@@ -6120,7 +7911,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D197" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="198">
@@ -6148,7 +7939,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D199" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="200">
@@ -6176,7 +7967,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D201" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="202">
@@ -6204,7 +7995,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D203" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="204">
@@ -6232,7 +8023,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D205" t="str">
-        <v>Loše fiksiran donji deo klupe,</v>
+        <v>Loše fiksiran donji deo klupe</v>
       </c>
     </row>
     <row r="206">
@@ -6246,7 +8037,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D206" t="str">
-        <v>problem sa preklapanjem naslona,</v>
+        <v>problem sa preklapanjem naslona</v>
       </c>
     </row>
     <row r="207">
@@ -6274,7 +8065,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D208" t="str">
-        <v>Oštećenja tapacirunga krova (nebo),</v>
+        <v>Oštećenja tapacirunga krova (nebo)</v>
       </c>
     </row>
     <row r="209">
@@ -6288,7 +8079,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D209" t="str">
-        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+        <v>ogrebotine na oblogama stubova (A, B, C)</v>
       </c>
     </row>
     <row r="210">
@@ -6302,7 +8093,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D210" t="str">
-        <v>labavi rukohvati na krovu,</v>
+        <v>labavi rukohvati na krovu</v>
       </c>
     </row>
     <row r="211">
@@ -6330,7 +8121,7 @@
         <v>Elektrika</v>
       </c>
       <c r="D212" t="str">
-        <v>Greška na instrument tabli, , ,</v>
+        <v>Greška na instrument tabli</v>
       </c>
     </row>
     <row r="213">
@@ -6386,7 +8177,7 @@
         <v>Rasveta</v>
       </c>
       <c r="D216" t="str">
-        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla</v>
       </c>
     </row>
     <row r="217">
@@ -6456,7 +8247,7 @@
         <v>Kamere i senzori</v>
       </c>
       <c r="D221" t="str">
-        <v>Labavost parking senzora (upali unutra), ,</v>
+        <v>Labavost parking senzora (upali unutra)</v>
       </c>
     </row>
     <row r="222">
@@ -6498,7 +8289,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D224" t="str">
-        <v>Labav pod gepeka, ,</v>
+        <v>Labav pod gepeka</v>
       </c>
     </row>
     <row r="225">
@@ -6526,7 +8317,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D226" t="str">
-        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica)</v>
       </c>
     </row>
     <row r="227">
@@ -6554,7 +8345,7 @@
         <v>Funkcionalni test</v>
       </c>
       <c r="D228" t="str">
-        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+        <v>Loš odziv multimedije (ekrana na dodir), .</v>
       </c>
     </row>
     <row r="229">
@@ -6610,7 +8401,7 @@
         <v>Ostalo</v>
       </c>
       <c r="D232" t="str">
-        <v>Prljavština na vozilu,, , .</v>
+        <v>Prljavština na vozilu, .</v>
       </c>
     </row>
     <row r="233">
@@ -6806,7 +8597,7 @@
         <v>Levo prednje krilo</v>
       </c>
       <c r="D246" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="247">
@@ -6848,7 +8639,7 @@
         <v>Desno prednje krilo</v>
       </c>
       <c r="D249" t="str">
-        <v>Ogrebotine,,</v>
+        <v>Ogrebotine</v>
       </c>
     </row>
     <row r="250">
@@ -6890,7 +8681,7 @@
         <v>Leva prednja vrata</v>
       </c>
       <c r="D252" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="253">
@@ -6946,7 +8737,7 @@
         <v>Desna prednja vrata</v>
       </c>
       <c r="D256" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="257">
@@ -7002,7 +8793,7 @@
         <v>Leva zadnja vrata</v>
       </c>
       <c r="D260" t="str">
-        <v>Loš zazor/poravnanje, , , .</v>
+        <v>Loš zazor/poravnanje, .</v>
       </c>
     </row>
     <row r="261">
@@ -7254,7 +9045,7 @@
         <v>Zadnji branik</v>
       </c>
       <c r="D278" t="str">
-        <v>ogrebotine pri dnu,</v>
+        <v>ogrebotine pri dnu</v>
       </c>
     </row>
     <row r="279">
@@ -7282,7 +9073,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D280" t="str">
-        <v>Teško zatvaranje,</v>
+        <v>Teško zatvaranje</v>
       </c>
     </row>
     <row r="281">
@@ -7310,7 +9101,7 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D282" t="str">
-        <v>visinska odstupanja,</v>
+        <v>visinska odstupanja</v>
       </c>
     </row>
     <row r="283">
@@ -7436,7 +9227,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D291" t="str">
-        <v>Ogrebotine od podizanja/spuštanja,</v>
+        <v>Ogrebotine od podizanja/spuštanja</v>
       </c>
     </row>
     <row r="292">
@@ -7450,7 +9241,7 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D292" t="str">
-        <v>zazor pri zatvaranju (prolaz vazduha),</v>
+        <v>zazor pri zatvaranju (prolaz vazduha)</v>
       </c>
     </row>
     <row r="293">
@@ -7478,7 +9269,7 @@
         <v>Motorni prostor</v>
       </c>
       <c r="D294" t="str">
-        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona)</v>
       </c>
     </row>
     <row r="295">
@@ -7534,7 +9325,7 @@
         <v>Podvozje</v>
       </c>
       <c r="D298" t="str">
-        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
+        <v>Curenje tečnosti na spojevima (menjač, karter)</v>
       </c>
     </row>
     <row r="299">
@@ -7590,7 +9381,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D302" t="str">
-        <v>Ogrebotine na alu-felnama, ,</v>
+        <v>Ogrebotine na alu-felnama</v>
       </c>
     </row>
     <row r="303">
@@ -7604,7 +9395,7 @@
         <v>Točkovi i gume</v>
       </c>
       <c r="D303" t="str">
-        <v>pogrešan smer rotacije gume,</v>
+        <v>pogrešan smer rotacije gume</v>
       </c>
     </row>
     <row r="304">
@@ -7646,7 +9437,7 @@
         <v>Instrument tabla</v>
       </c>
       <c r="D306" t="str">
-        <v>Loš zazor na spojevima plastika,, , .</v>
+        <v>Loš zazor na spojevima plastika, .</v>
       </c>
     </row>
     <row r="307">
@@ -7702,7 +9493,7 @@
         <v>Centralna konzola</v>
       </c>
       <c r="D310" t="str">
-        <v>Labavost naslona za ruku, , ,.</v>
+        <v>Labavost naslona za ruku, .</v>
       </c>
     </row>
     <row r="311">
@@ -7758,7 +9549,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D314" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="315">
@@ -7786,7 +9577,7 @@
         <v>Sedište vozača</v>
       </c>
       <c r="D316" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="317">
@@ -7814,7 +9605,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D318" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Oštećenje šavova, .</v>
       </c>
     </row>
     <row r="319">
@@ -7842,7 +9633,7 @@
         <v>Sedište suvozača</v>
       </c>
       <c r="D320" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro)</v>
       </c>
     </row>
     <row r="321">
@@ -7870,7 +9661,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D322" t="str">
-        <v>Loše fiksiran donji deo klupe,</v>
+        <v>Loše fiksiran donji deo klupe</v>
       </c>
     </row>
     <row r="323">
@@ -7884,7 +9675,7 @@
         <v>Zadnja sedišta</v>
       </c>
       <c r="D323" t="str">
-        <v>problem sa preklapanjem naslona,</v>
+        <v>problem sa preklapanjem naslona</v>
       </c>
     </row>
     <row r="324">
@@ -7912,7 +9703,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D325" t="str">
-        <v>Oštećenja tapacirunga krova (nebo),</v>
+        <v>Oštećenja tapacirunga krova (nebo)</v>
       </c>
     </row>
     <row r="326">
@@ -7926,7 +9717,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D326" t="str">
-        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+        <v>ogrebotine na oblogama stubova (A, B, C)</v>
       </c>
     </row>
     <row r="327">
@@ -7940,7 +9731,7 @@
         <v>Enterijer</v>
       </c>
       <c r="D327" t="str">
-        <v>labavi rukohvati na krovu,</v>
+        <v>labavi rukohvati na krovu</v>
       </c>
     </row>
     <row r="328">
@@ -7968,7 +9759,7 @@
         <v>Elektrika</v>
       </c>
       <c r="D329" t="str">
-        <v>Greška na instrument tabli, , ,</v>
+        <v>Greška na instrument tabli</v>
       </c>
     </row>
     <row r="330">
@@ -8024,7 +9815,7 @@
         <v>Rasveta</v>
       </c>
       <c r="D333" t="str">
-        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla</v>
       </c>
     </row>
     <row r="334">
@@ -8094,7 +9885,7 @@
         <v>Kamere i senzori</v>
       </c>
       <c r="D338" t="str">
-        <v>Labavost parking senzora (upali unutra), ,</v>
+        <v>Labavost parking senzora (upali unutra)</v>
       </c>
     </row>
     <row r="339">
@@ -8136,7 +9927,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D341" t="str">
-        <v>Labav pod gepeka, ,</v>
+        <v>Labav pod gepeka</v>
       </c>
     </row>
     <row r="342">
@@ -8164,7 +9955,7 @@
         <v>Prtljažni prostor</v>
       </c>
       <c r="D343" t="str">
-        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica)</v>
       </c>
     </row>
     <row r="344">
@@ -8192,7 +9983,7 @@
         <v>Funkcionalni test</v>
       </c>
       <c r="D345" t="str">
-        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+        <v>Loš odziv multimedije (ekrana na dodir), .</v>
       </c>
     </row>
     <row r="346">
@@ -8248,7 +10039,7 @@
         <v>Ostalo</v>
       </c>
       <c r="D349" t="str">
-        <v>Prljavština na vozilu,, , .</v>
+        <v>Prljavština na vozilu, .</v>
       </c>
     </row>
     <row r="350">
@@ -8294,7 +10085,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D352"/>
   </ignoredErrors>
